--- a/ESP32_Liste.xlsx
+++ b/ESP32_Liste.xlsx
@@ -827,8 +827,8 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101001082DE17B8F5754483FA365BAF249E6A" ma:contentTypeVersion="11" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="afe4dfe494d44b11ec5c397610c3ce29">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6253c58b-4718-4cbc-9c45-cb3c01f1fbe9" xmlns:ns3="90b8c57a-dabd-4666-984b-58c86236ec7c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="cb6acc7f4796fd37ecbfd926f69ebdb9" ns2:_="" ns3:_="">
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x0101001082DE17B8F5754483FA365BAF249E6A" ma:contentTypeVersion="12" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="f5fd9a64df4072b56d1ca1621a9f064e">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="6253c58b-4718-4cbc-9c45-cb3c01f1fbe9" xmlns:ns3="90b8c57a-dabd-4666-984b-58c86236ec7c" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="1a659212f8868f680a6ccf77fce12727" ns2:_="" ns3:_="">
     <xsd:import namespace="6253c58b-4718-4cbc-9c45-cb3c01f1fbe9"/>
     <xsd:import namespace="90b8c57a-dabd-4666-984b-58c86236ec7c"/>
     <xsd:element name="properties">
@@ -847,6 +847,7 @@
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -904,6 +905,11 @@
     <xsd:element name="MediaServiceLocation" ma:index="18" nillable="true" ma:displayName="Location" ma:indexed="true" ma:internalName="MediaServiceLocation" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="19" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
       </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
@@ -1042,7 +1048,7 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0EE91775-9F59-4E15-B93A-71038C195AB2}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C6E52AD1-1FE9-484C-8902-DBA3CB65A838}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
